--- a/builder/src/test/resources/eoTest.xlsx
+++ b/builder/src/test/resources/eoTest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/werner.diwischek/dev/elasticobjects/builder/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DAE222-B1C9-554C-859F-79456F525190}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DE7DA9-4E2E-974B-8E77-5CF2FAC72BA7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6620" yWindow="2660" windowWidth="28240" windowHeight="17100" activeTab="1" xr2:uid="{1E8B47EF-5738-BE4A-AAD2-1678499A82C4}"/>
+    <workbookView xWindow="9800" yWindow="460" windowWidth="28240" windowHeight="17100" xr2:uid="{1E8B47EF-5738-BE4A-AAD2-1678499A82C4}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelConfig" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ModelConfig!$A$1:$N$3</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -241,9 +240,6 @@
     <t>hostConfigKey</t>
   </si>
   <si>
-    <t>{"create": true,  "shapeType": "BEAN"}</t>
-  </si>
-  <si>
     <t>ATestObject</t>
   </si>
   <si>
@@ -320,6 +316,9 @@
   </si>
   <si>
     <t>An ArrayList</t>
+  </si>
+  <si>
+    <t>{"create": true}</t>
   </si>
 </sst>
 </file>
@@ -767,7 +766,7 @@
     </row>
     <row r="2" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>32</v>
@@ -779,7 +778,7 @@
         <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>11</v>
@@ -795,7 +794,7 @@
         <v>ATestObject</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>28</v>
@@ -806,7 +805,7 @@
     </row>
     <row r="3" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
@@ -818,7 +817,7 @@
         <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>11</v>
@@ -834,7 +833,7 @@
         <v>ATestSubObject</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>28</v>
@@ -854,13 +853,13 @@
         <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>29</v>
@@ -870,7 +869,7 @@
         <v>Date</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -881,13 +880,13 @@
         <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>30</v>
@@ -897,7 +896,7 @@
         <v>Integer</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -908,13 +907,13 @@
         <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>29</v>
@@ -924,7 +923,7 @@
         <v>ArrayList</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -935,13 +934,13 @@
         <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>29</v>
@@ -951,7 +950,7 @@
         <v>HashMap</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -962,13 +961,13 @@
         <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>30</v>
@@ -978,7 +977,7 @@
         <v>String</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1045,7 +1044,7 @@
     </row>
     <row r="2" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
@@ -1054,10 +1053,10 @@
         <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -1070,7 +1069,7 @@
     </row>
     <row r="3" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
         <v>39</v>
@@ -1079,7 +1078,7 @@
         <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="1" t="str">
         <f>A3</f>
@@ -1096,7 +1095,7 @@
     </row>
     <row r="4" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
         <v>39</v>
@@ -1122,7 +1121,7 @@
     </row>
     <row r="5" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
@@ -1147,7 +1146,7 @@
     </row>
     <row r="6" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
         <v>39</v>
@@ -1173,7 +1172,7 @@
     </row>
     <row r="7" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
         <v>39</v>
@@ -1198,7 +1197,7 @@
     </row>
     <row r="8" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
         <v>39</v>
@@ -1226,7 +1225,7 @@
     </row>
     <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
         <v>39</v>
@@ -1924,7 +1923,7 @@
     </row>
     <row r="2" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>34</v>
@@ -1942,7 +1941,7 @@
         <v>44</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>48</v>
@@ -1959,7 +1958,7 @@
     </row>
     <row r="3" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>34</v>
@@ -1977,7 +1976,7 @@
         <v>44</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>47</v>
@@ -1994,7 +1993,7 @@
     </row>
     <row r="4" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>34</v>
@@ -2012,7 +2011,7 @@
         <v>44</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>49</v>
@@ -2029,7 +2028,7 @@
     </row>
     <row r="5" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>34</v>
@@ -2047,7 +2046,7 @@
         <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>50</v>
@@ -2064,7 +2063,7 @@
     </row>
     <row r="6" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>34</v>
@@ -2082,7 +2081,7 @@
         <v>44</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>51</v>
@@ -2099,7 +2098,7 @@
     </row>
     <row r="7" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>31</v>
@@ -2117,7 +2116,7 @@
         <v>44</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>51</v>
